--- a/product_selector_out/STM32F302.xlsx
+++ b/product_selector_out/STM32F302.xlsx
@@ -1472,7 +1472,7 @@
       </c>
       <c r="AD13" s="4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE13" s="4" t="inlineStr">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="AD14" s="4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>51</t>
         </is>
       </c>
       <c r="AE14" s="4" t="inlineStr">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="AD15" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE15" s="4" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="AD16" s="4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>51</t>
         </is>
       </c>
       <c r="AE16" s="4" t="inlineStr">
@@ -3107,7 +3107,7 @@
       </c>
       <c r="AD18" s="4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>51</t>
         </is>
       </c>
       <c r="AE18" s="4" t="inlineStr">
@@ -3434,7 +3434,7 @@
       </c>
       <c r="AD19" s="4" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>115</t>
         </is>
       </c>
       <c r="AE19" s="4" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="AD20" s="4" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>115</t>
         </is>
       </c>
       <c r="AE20" s="4" t="inlineStr">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="AD25" s="4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE25" s="4" t="inlineStr">
@@ -6050,7 +6050,7 @@
       </c>
       <c r="AD27" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE27" s="4" t="inlineStr">
@@ -6704,7 +6704,7 @@
       </c>
       <c r="AD29" s="4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>51</t>
         </is>
       </c>
       <c r="AE29" s="4" t="inlineStr">
@@ -7906,14 +7906,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U13" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V13" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W13" s="8" t="inlineStr">
@@ -7936,9 +7936,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA13" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB13" s="6" t="inlineStr">
@@ -7991,9 +7991,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AL13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM13" s="8" t="inlineStr">
@@ -8263,9 +8263,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA14" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB14" s="6" t="inlineStr">
@@ -8560,14 +8560,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U15" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V15" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W15" s="8" t="inlineStr">
@@ -8590,9 +8590,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA15" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB15" s="6" t="inlineStr">
@@ -8645,9 +8645,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AL15" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM15" s="8" t="inlineStr">
@@ -8887,14 +8887,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U16" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V16" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W16" s="8" t="inlineStr">
@@ -8917,9 +8917,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA16" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB16" s="6" t="inlineStr">
@@ -8972,9 +8972,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AL16" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM16" s="8" t="inlineStr">
@@ -9244,9 +9244,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA17" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB17" s="6" t="inlineStr">
@@ -9571,9 +9571,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA18" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB18" s="6" t="inlineStr">
@@ -9898,9 +9898,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA19" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB19" s="6" t="inlineStr">
@@ -10225,9 +10225,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA20" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB20" s="6" t="inlineStr">
@@ -11206,9 +11206,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA23" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB23" s="6" t="inlineStr">
@@ -11830,14 +11830,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U25" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V25" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U25" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V25" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W25" s="8" t="inlineStr">
@@ -11860,9 +11860,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA25" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA25" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB25" s="6" t="inlineStr">
@@ -11915,9 +11915,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AL25" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM25" s="8" t="inlineStr">
@@ -12484,14 +12484,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U27" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V27" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U27" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V27" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W27" s="8" t="inlineStr">
@@ -12514,9 +12514,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA27" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA27" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB27" s="6" t="inlineStr">
@@ -12569,9 +12569,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AL27" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM27" s="8" t="inlineStr">
@@ -13138,14 +13138,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U29" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V29" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U29" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V29" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W29" s="8" t="inlineStr">
@@ -13168,9 +13168,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA29" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA29" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB29" s="6" t="inlineStr">
@@ -13223,9 +13223,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AL29" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL29" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM29" s="8" t="inlineStr">

--- a/product_selector_out/STM32F302.xlsx
+++ b/product_selector_out/STM32F302.xlsx
@@ -8323,9 +8323,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM14" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN14" s="6" t="inlineStr">
@@ -9304,9 +9304,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM17" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN17" s="6" t="inlineStr">
@@ -9631,9 +9631,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM18" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN18" s="6" t="inlineStr">
@@ -9958,9 +9958,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM19" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN19" s="6" t="inlineStr">
@@ -10285,9 +10285,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM20" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN20" s="6" t="inlineStr">
@@ -11266,9 +11266,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM23" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN23" s="6" t="inlineStr">

--- a/product_selector_out/STM32F302.xlsx
+++ b/product_selector_out/STM32F302.xlsx
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM29"/>
+  <dimension ref="A1:BN29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.51953125" customWidth="1" min="1" max="1"/>
@@ -573,7 +573,8 @@
     <col width="21.765625" customWidth="1" min="62" max="62"/>
     <col width="18" customWidth="1" min="63" max="63"/>
     <col width="18" customWidth="1" min="64" max="64"/>
-    <col width="52" customWidth="1" min="65" max="65"/>
+    <col width="18" customWidth="1" min="65" max="65"/>
+    <col width="52" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -901,6 +902,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -996,6 +1002,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1320,6 +1327,11 @@
       </c>
       <c r="BM12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f302cb.pdf</t>
         </is>
       </c>
@@ -1647,6 +1659,11 @@
       </c>
       <c r="BM13" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN13" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f302c6.pdf</t>
         </is>
       </c>
@@ -1974,6 +1991,11 @@
       </c>
       <c r="BM14" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN14" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f302rd.pdf</t>
         </is>
       </c>
@@ -2301,6 +2323,11 @@
       </c>
       <c r="BM15" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f302c6.pdf</t>
         </is>
       </c>
@@ -2628,6 +2655,11 @@
       </c>
       <c r="BM16" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN16" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f302c6.pdf</t>
         </is>
       </c>
@@ -2955,6 +2987,11 @@
       </c>
       <c r="BM17" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN17" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f302rd.pdf</t>
         </is>
       </c>
@@ -3282,6 +3319,11 @@
       </c>
       <c r="BM18" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN18" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f302rd.pdf</t>
         </is>
       </c>
@@ -3609,6 +3651,11 @@
       </c>
       <c r="BM19" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN19" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f302rd.pdf</t>
         </is>
       </c>
@@ -3936,6 +3983,11 @@
       </c>
       <c r="BM20" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN20" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f302rd.pdf</t>
         </is>
       </c>
@@ -4263,6 +4315,11 @@
       </c>
       <c r="BM21" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN21" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f302cb.pdf</t>
         </is>
       </c>
@@ -4590,6 +4647,11 @@
       </c>
       <c r="BM22" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN22" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f302cb.pdf</t>
         </is>
       </c>
@@ -4917,6 +4979,11 @@
       </c>
       <c r="BM23" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN23" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f302rd.pdf</t>
         </is>
       </c>
@@ -5244,6 +5311,11 @@
       </c>
       <c r="BM24" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN24" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f302cb.pdf</t>
         </is>
       </c>
@@ -5571,6 +5643,11 @@
       </c>
       <c r="BM25" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN25" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f302c6.pdf</t>
         </is>
       </c>
@@ -5898,6 +5975,11 @@
       </c>
       <c r="BM26" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN26" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f302cb.pdf</t>
         </is>
       </c>
@@ -6225,6 +6307,11 @@
       </c>
       <c r="BM27" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN27" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f302c6.pdf</t>
         </is>
       </c>
@@ -6552,6 +6639,11 @@
       </c>
       <c r="BM28" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN28" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f302cb.pdf</t>
         </is>
       </c>
@@ -6879,12 +6971,17 @@
       </c>
       <c r="BM29" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN29" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f302c6.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="64">
+  <mergeCells count="65">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -6905,16 +7002,14 @@
     <mergeCell ref="BA10:BA11"/>
     <mergeCell ref="BG10:BG11"/>
     <mergeCell ref="Q10:Q11"/>
-    <mergeCell ref="A1:BM8"/>
     <mergeCell ref="AR10:AR11"/>
+    <mergeCell ref="AT10:AT11"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="AT10:AT11"/>
+    <mergeCell ref="BI10:BI11"/>
     <mergeCell ref="AV10:AV11"/>
-    <mergeCell ref="A9:BM9"/>
     <mergeCell ref="BB10:BB11"/>
-    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="BD10:BD11"/>
-    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="Y10:Z10"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
@@ -6927,6 +7022,7 @@
     <mergeCell ref="AQ10:AQ11"/>
     <mergeCell ref="AW10:AW11"/>
     <mergeCell ref="BH10:BH11"/>
+    <mergeCell ref="BN10:BN11"/>
     <mergeCell ref="AY10:AY11"/>
     <mergeCell ref="BK10:BK11"/>
     <mergeCell ref="A10:A11"/>
@@ -6946,7 +7042,9 @@
     <mergeCell ref="U10:V10"/>
     <mergeCell ref="AG10:AG11"/>
     <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A9:BN9"/>
     <mergeCell ref="H10:H11"/>
+    <mergeCell ref="A1:BN8"/>
     <mergeCell ref="T10:T11"/>
     <mergeCell ref="J10:J11"/>
   </mergeCells>
@@ -6981,7 +7079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM29"/>
+  <dimension ref="A1:BN29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7049,6 +7147,7 @@
     <col width="16" customWidth="1" min="63" max="63"/>
     <col width="16" customWidth="1" min="64" max="64"/>
     <col width="16" customWidth="1" min="65" max="65"/>
+    <col width="16" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7382,6 +7481,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -7477,6 +7581,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -7799,7 +7904,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM12" s="6" t="inlineStr">
+      <c r="BM12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8126,7 +8236,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM13" s="6" t="inlineStr">
+      <c r="BM13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN13" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8453,7 +8568,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM14" s="6" t="inlineStr">
+      <c r="BM14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN14" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8780,7 +8900,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM15" s="6" t="inlineStr">
+      <c r="BM15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9107,7 +9232,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM16" s="6" t="inlineStr">
+      <c r="BM16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN16" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9434,7 +9564,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM17" s="6" t="inlineStr">
+      <c r="BM17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN17" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9761,7 +9896,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM18" s="6" t="inlineStr">
+      <c r="BM18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN18" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10088,7 +10228,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM19" s="6" t="inlineStr">
+      <c r="BM19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN19" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10415,7 +10560,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM20" s="6" t="inlineStr">
+      <c r="BM20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN20" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10742,7 +10892,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM21" s="6" t="inlineStr">
+      <c r="BM21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN21" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11069,7 +11224,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM22" s="6" t="inlineStr">
+      <c r="BM22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN22" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11396,7 +11556,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM23" s="6" t="inlineStr">
+      <c r="BM23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN23" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11723,7 +11888,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM24" s="6" t="inlineStr">
+      <c r="BM24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN24" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12050,7 +12220,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM25" s="6" t="inlineStr">
+      <c r="BM25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN25" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12377,7 +12552,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM26" s="6" t="inlineStr">
+      <c r="BM26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN26" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12704,7 +12884,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM27" s="6" t="inlineStr">
+      <c r="BM27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN27" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -13031,7 +13216,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM28" s="6" t="inlineStr">
+      <c r="BM28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN28" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -13358,7 +13548,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM29" s="6" t="inlineStr">
+      <c r="BM29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN29" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -13366,8 +13561,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:BM9"/>
-    <mergeCell ref="A1:BM8"/>
+    <mergeCell ref="A9:BN9"/>
+    <mergeCell ref="A1:BN8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
